--- a/artfynd/A 33866-2021 artfynd.xlsx
+++ b/artfynd/A 33866-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33866-2021 artfynd.xlsx
+++ b/artfynd/A 33866-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4149790</v>
+        <v>2864590</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ottersäng, 775 m O, Vrm</t>
+          <t>Jönsberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>429176.0081451457</v>
+        <v>429175</v>
       </c>
       <c r="R2" t="n">
-        <v>6609009.700596027</v>
+        <v>6609345</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-05-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-05-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Något fuktig hyggeskant mot skogsbryn</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,22 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Crister Albinsson, Stina Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75348985</v>
+        <v>4149790</v>
       </c>
       <c r="B3" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,22 +812,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korridor, Skived - Molkom, Vrm</t>
+          <t>Ottersäng, 775 m O, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429330.9177027603</v>
+        <v>429176</v>
       </c>
       <c r="R3" t="n">
-        <v>6609265.912970147</v>
+        <v>6609010</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-05-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>JMN0029, Calluna AB på uppdrag av Rejlers Sverige AB.</t>
+          <t>2013-05-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,18 +873,245 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Något fuktig hyggeskant mot skogsbryn</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75348985</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korridor, Skived - Molkom, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>429331</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6609266</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>JMN0029, Calluna AB på uppdrag av Rejlers Sverige AB.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Jonas Mattsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Jonas Mattsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5927718</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jönsberget i S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>429181</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6609336</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-07-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-07-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granskog på hyperit</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
